--- a/data/auxiliar.xlsx
+++ b/data/auxiliar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailadventistas-my.sharepoint.com/personal/daniel_llaca_adventistas_org/Documents/INFORME JUNTAS/MENSUAL Y DIARIO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EB41F0-0459-4765-B2C0-ADD2A7224810}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E58AADA7-1ADE-4098-B929-9D543BD67CB8}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2580" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9F8F2C5A-F36E-41DE-A9AC-0765B5EE11E5}"/>
+    <workbookView xWindow="-38520" yWindow="-2580" windowWidth="38640" windowHeight="21120" xr2:uid="{9F8F2C5A-F36E-41DE-A9AC-0765B5EE11E5}"/>
   </bookViews>
   <sheets>
     <sheet name="INGRESOS" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="40">
   <si>
     <t>Entidad</t>
   </si>
@@ -596,16 +596,16 @@
         <v>7322</v>
       </c>
       <c r="B2">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -614,7 +614,7 @@
         <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -622,25 +622,25 @@
         <v>7322</v>
       </c>
       <c r="B3">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -651,22 +651,22 @@
         <v>121411</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -674,25 +674,25 @@
         <v>7322</v>
       </c>
       <c r="B5">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -700,25 +700,25 @@
         <v>7322</v>
       </c>
       <c r="B6">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -726,25 +726,25 @@
         <v>7322</v>
       </c>
       <c r="B7">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -752,25 +752,25 @@
         <v>7322</v>
       </c>
       <c r="B8">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -778,25 +778,25 @@
         <v>7322</v>
       </c>
       <c r="B9">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -807,22 +807,22 @@
         <v>122011</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -830,19 +830,19 @@
         <v>7322</v>
       </c>
       <c r="B11">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -856,25 +856,25 @@
         <v>7322</v>
       </c>
       <c r="B12">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -885,22 +885,22 @@
         <v>121411</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -908,19 +908,19 @@
         <v>7322</v>
       </c>
       <c r="B14">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
         <v>12</v>
@@ -934,25 +934,25 @@
         <v>7322</v>
       </c>
       <c r="B15">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="s">
         <v>12</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -960,28 +960,25 @@
         <v>7322</v>
       </c>
       <c r="B16">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
       <c r="F16" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -989,7 +986,7 @@
         <v>7322</v>
       </c>
       <c r="B17">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -998,10 +995,10 @@
         <v>11</v>
       </c>
       <c r="F17" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17" t="s">
         <v>12</v>
@@ -1015,25 +1012,25 @@
         <v>7322</v>
       </c>
       <c r="B18">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I18" t="s">
         <v>12</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1041,25 +1038,25 @@
         <v>7322</v>
       </c>
       <c r="B19">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I19" t="s">
         <v>12</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1067,25 +1064,28 @@
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121511</v>
+        <v>121311</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
       <c r="F20" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1093,28 +1093,25 @@
         <v>7322</v>
       </c>
       <c r="B21">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
-        <v>33</v>
-      </c>
       <c r="F21" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H21">
+        <v>7</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" t="s">
         <v>17</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1122,10 +1119,10 @@
         <v>7322</v>
       </c>
       <c r="B22">
-        <v>121411</v>
+        <v>121111</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1134,13 +1131,13 @@
         <v>46147</v>
       </c>
       <c r="H22">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I22" t="s">
         <v>12</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1148,28 +1145,25 @@
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
-      <c r="E23" t="s">
-        <v>34</v>
-      </c>
       <c r="F23" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H23">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J23" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1180,16 +1174,16 @@
         <v>121511</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H24">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I24" t="s">
         <v>12</v>
@@ -1203,25 +1197,28 @@
         <v>7322</v>
       </c>
       <c r="B25">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
       <c r="F25" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H25">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1229,7 +1226,7 @@
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -1238,16 +1235,16 @@
         <v>11</v>
       </c>
       <c r="F26" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H26">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
         <v>12</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1255,7 +1252,7 @@
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1263,17 +1260,20 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
       <c r="F27" s="1">
         <v>46146</v>
       </c>
       <c r="H27">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1281,19 +1281,19 @@
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I28" t="s">
         <v>12</v>
@@ -1307,7 +1307,7 @@
         <v>7322</v>
       </c>
       <c r="B29">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1315,20 +1315,17 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" t="s">
-        <v>35</v>
-      </c>
       <c r="F29" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1336,25 +1333,25 @@
         <v>7322</v>
       </c>
       <c r="B30">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="I30" t="s">
         <v>12</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1362,25 +1359,25 @@
         <v>7322</v>
       </c>
       <c r="B31">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="I31" t="s">
         <v>12</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1388,19 +1385,19 @@
         <v>7322</v>
       </c>
       <c r="B32">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H32">
         <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1">
-        <v>46144</v>
-      </c>
-      <c r="H32">
-        <v>2</v>
       </c>
       <c r="I32" t="s">
         <v>12</v>
@@ -1414,7 +1411,7 @@
         <v>7322</v>
       </c>
       <c r="B33">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1422,17 +1419,20 @@
       <c r="D33" t="s">
         <v>11</v>
       </c>
+      <c r="E33" t="s">
+        <v>35</v>
+      </c>
       <c r="F33" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1440,19 +1440,19 @@
         <v>7322</v>
       </c>
       <c r="B34">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H34">
         <v>1</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1">
-        <v>46143</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
       </c>
       <c r="I34" t="s">
         <v>12</v>
@@ -1466,7 +1466,7 @@
         <v>7322</v>
       </c>
       <c r="B35">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1474,33 +1474,125 @@
       <c r="D35" t="s">
         <v>11</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7322</v>
+      </c>
+      <c r="B36">
+        <v>121411</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>7322</v>
+      </c>
+      <c r="B37">
+        <v>122011</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>7322</v>
+      </c>
+      <c r="B38">
+        <v>122011</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38" t="s">
+        <v>12</v>
+      </c>
+      <c r="J38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>7322</v>
+      </c>
+      <c r="B39">
+        <v>121311</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F39" s="1">
         <v>46143</v>
       </c>
-      <c r="H35">
+      <c r="H39">
         <v>1</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I39" t="s">
         <v>32</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J39" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F40" s="1"/>
@@ -1750,16 +1842,16 @@
         <v>7322</v>
       </c>
       <c r="B2">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1768,7 +1860,7 @@
         <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1776,25 +1868,25 @@
         <v>7322</v>
       </c>
       <c r="B3">
-        <v>121311</v>
+        <v>121411</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1802,10 +1894,10 @@
         <v>7322</v>
       </c>
       <c r="B4">
-        <v>121411</v>
+        <v>121111</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1814,13 +1906,13 @@
         <v>46153</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1831,22 +1923,22 @@
         <v>122011</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1854,16 +1946,16 @@
         <v>7322</v>
       </c>
       <c r="B6">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1872,7 +1964,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1880,25 +1972,25 @@
         <v>7322</v>
       </c>
       <c r="B7">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46150</v>
-      </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
       <c r="I7" t="s">
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1906,25 +1998,25 @@
         <v>7322</v>
       </c>
       <c r="B8">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1932,7 +2024,7 @@
         <v>7322</v>
       </c>
       <c r="B9">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1941,7 +2033,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -1950,7 +2042,7 @@
         <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1958,25 +2050,25 @@
         <v>7322</v>
       </c>
       <c r="B10">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1987,16 +2079,16 @@
         <v>121411</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -2010,25 +2102,25 @@
         <v>7322</v>
       </c>
       <c r="B12">
-        <v>121511</v>
+        <v>122011</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H12">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2036,25 +2128,25 @@
         <v>7322</v>
       </c>
       <c r="B13">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,28 +2154,25 @@
         <v>7322</v>
       </c>
       <c r="B14">
-        <v>121311</v>
+        <v>121411</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2091,25 +2180,25 @@
         <v>7322</v>
       </c>
       <c r="B15">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I15" t="s">
         <v>12</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2117,7 +2206,7 @@
         <v>7322</v>
       </c>
       <c r="B16">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -2126,16 +2215,16 @@
         <v>18</v>
       </c>
       <c r="F16" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I16" t="s">
         <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2143,25 +2232,28 @@
         <v>7322</v>
       </c>
       <c r="B17">
-        <v>121511</v>
+        <v>121311</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
       <c r="F17" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2169,28 +2261,25 @@
         <v>7322</v>
       </c>
       <c r="B18">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="E18" t="s">
-        <v>38</v>
-      </c>
       <c r="F18" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2198,10 +2287,10 @@
         <v>7322</v>
       </c>
       <c r="B19">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -2210,13 +2299,13 @@
         <v>46147</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I19" t="s">
         <v>12</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2224,10 +2313,10 @@
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2236,13 +2325,13 @@
         <v>46147</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I20" t="s">
         <v>12</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2250,7 +2339,7 @@
         <v>7322</v>
       </c>
       <c r="B21">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2258,17 +2347,20 @@
       <c r="D21" t="s">
         <v>18</v>
       </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
       <c r="F21" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2279,22 +2371,22 @@
         <v>121411</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H22">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="I22" t="s">
         <v>12</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2302,28 +2394,25 @@
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46147</v>
+      </c>
+      <c r="H23">
         <v>1</v>
       </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46146</v>
-      </c>
-      <c r="H23">
-        <v>4</v>
-      </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2331,10 +2420,10 @@
         <v>7322</v>
       </c>
       <c r="B24">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -2343,13 +2432,13 @@
         <v>46146</v>
       </c>
       <c r="H24">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="I24" t="s">
         <v>12</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2357,10 +2446,10 @@
         <v>7322</v>
       </c>
       <c r="B25">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -2369,13 +2458,13 @@
         <v>46146</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I25" t="s">
         <v>12</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2383,25 +2472,28 @@
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
       <c r="F26" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2409,25 +2501,25 @@
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
         <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2435,7 +2527,7 @@
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2444,16 +2536,16 @@
         <v>18</v>
       </c>
       <c r="F28" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I28" t="s">
         <v>12</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2464,13 +2556,13 @@
         <v>122011</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -2483,13 +2575,82 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F30" s="1"/>
+      <c r="A30">
+        <v>7322</v>
+      </c>
+      <c r="B30">
+        <v>121411</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F31" s="1"/>
+      <c r="A31">
+        <v>7322</v>
+      </c>
+      <c r="B31">
+        <v>121111</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F32" s="1"/>
+      <c r="A32">
+        <v>7322</v>
+      </c>
+      <c r="B32">
+        <v>122011</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F33" s="1"/>

--- a/data/auxiliar.xlsx
+++ b/data/auxiliar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailadventistas-my.sharepoint.com/personal/daniel_llaca_adventistas_org/Documents/INFORME JUNTAS/MENSUAL Y DIARIO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E58AADA7-1ADE-4098-B929-9D543BD67CB8}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABF272D-2AE5-4215-B781-416F3BE4B778}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-2580" windowWidth="38640" windowHeight="21120" xr2:uid="{9F8F2C5A-F36E-41DE-A9AC-0765B5EE11E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="70">
   <si>
     <t>Entidad</t>
   </si>
@@ -161,13 +161,103 @@
   </si>
   <si>
     <t>Jose Carrasco Correa</t>
+  </si>
+  <si>
+    <t>RV 27</t>
+  </si>
+  <si>
+    <t>RV 16</t>
+  </si>
+  <si>
+    <t>RV 26</t>
+  </si>
+  <si>
+    <t>RV 15</t>
+  </si>
+  <si>
+    <t>RV 14</t>
+  </si>
+  <si>
+    <t>RV 25</t>
+  </si>
+  <si>
+    <t>RV 24</t>
+  </si>
+  <si>
+    <t>RV 13</t>
+  </si>
+  <si>
+    <t>RV 12</t>
+  </si>
+  <si>
+    <t>RV 23</t>
+  </si>
+  <si>
+    <t>RV 22</t>
+  </si>
+  <si>
+    <t>RV 11</t>
+  </si>
+  <si>
+    <t>RV 10</t>
+  </si>
+  <si>
+    <t>RV 21</t>
+  </si>
+  <si>
+    <t>RV 20</t>
+  </si>
+  <si>
+    <t>RV 9</t>
+  </si>
+  <si>
+    <t>RV 19</t>
+  </si>
+  <si>
+    <t>RV 38</t>
+  </si>
+  <si>
+    <t>RV 37</t>
+  </si>
+  <si>
+    <t>RV 36</t>
+  </si>
+  <si>
+    <t>RV 35</t>
+  </si>
+  <si>
+    <t>RV 34</t>
+  </si>
+  <si>
+    <t>RV 33</t>
+  </si>
+  <si>
+    <t>RV 32</t>
+  </si>
+  <si>
+    <t>RV 31</t>
+  </si>
+  <si>
+    <t>RV 30</t>
+  </si>
+  <si>
+    <t>RV 18</t>
+  </si>
+  <si>
+    <t>RV 17</t>
+  </si>
+  <si>
+    <t>RV 29</t>
+  </si>
+  <si>
+    <t>RV 28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,9 +641,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED6012F-B295-4163-9591-AE6F2542A3AA}">
   <dimension ref="A1:L103"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,7 +681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7322</v>
       </c>
@@ -599,16 +689,16 @@
         <v>121111</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -617,47 +707,47 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7322</v>
       </c>
       <c r="B3">
+        <v>121411</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46155</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>7322</v>
+      </c>
+      <c r="B4">
         <v>121311</v>
       </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46154</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>7322</v>
-      </c>
-      <c r="B4">
-        <v>121411</v>
-      </c>
       <c r="C4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -666,119 +756,122 @@
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7322</v>
       </c>
       <c r="B5">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7322</v>
       </c>
       <c r="B6">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
       <c r="F6" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7322</v>
+      </c>
+      <c r="B7">
+        <v>121111</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46154</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7322</v>
+      </c>
+      <c r="B8">
+        <v>121311</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46154</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7">
-        <v>7322</v>
-      </c>
-      <c r="B7">
-        <v>122011</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46153</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
-        <v>7322</v>
-      </c>
-      <c r="B8">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7322</v>
+      </c>
+      <c r="B9">
         <v>121411</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46153</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
-        <v>7322</v>
-      </c>
-      <c r="B9">
-        <v>122011</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -787,97 +880,100 @@
         <v>12</v>
       </c>
       <c r="F9" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7322</v>
       </c>
       <c r="B10">
+        <v>121111</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7322</v>
+      </c>
+      <c r="B11">
+        <v>121311</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7322</v>
+      </c>
+      <c r="B12">
         <v>122011</v>
       </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46151</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11">
-        <v>7322</v>
-      </c>
-      <c r="B11">
-        <v>121411</v>
-      </c>
-      <c r="C11">
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H12">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46151</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12">
-        <v>7322</v>
-      </c>
-      <c r="B12">
-        <v>121111</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46150</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>7322</v>
       </c>
@@ -885,25 +981,25 @@
         <v>121411</v>
       </c>
       <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H13">
         <v>7</v>
       </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46150</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
       <c r="I13" t="s">
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7322</v>
       </c>
@@ -911,103 +1007,109 @@
         <v>122011</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
       <c r="F14" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7322</v>
       </c>
       <c r="B15">
-        <v>121511</v>
+        <v>122011</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
       <c r="F15" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>7322</v>
       </c>
       <c r="B16">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46151</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>7322</v>
+      </c>
+      <c r="B17">
+        <v>121111</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H17">
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
-      <c r="I16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>7322</v>
-      </c>
-      <c r="B17">
-        <v>121411</v>
-      </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H17">
-        <v>6</v>
-      </c>
       <c r="I17" t="s">
         <v>13</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>7322</v>
       </c>
@@ -1015,80 +1117,80 @@
         <v>121411</v>
       </c>
       <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>7322</v>
+      </c>
+      <c r="B19">
+        <v>122011</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H19">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H18">
-        <v>7</v>
-      </c>
-      <c r="I18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19">
-        <v>7322</v>
-      </c>
-      <c r="B19">
-        <v>121111</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121311</v>
+        <v>121511</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
       <c r="F20" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7322</v>
       </c>
@@ -1096,56 +1198,59 @@
         <v>122011</v>
       </c>
       <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46149</v>
+      </c>
+      <c r="H21">
         <v>6</v>
       </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H21">
-        <v>7</v>
-      </c>
       <c r="I21" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7322</v>
       </c>
       <c r="B22">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -1154,45 +1259,45 @@
         <v>12</v>
       </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H23">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I23" t="s">
         <v>13</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7322</v>
       </c>
       <c r="B24">
-        <v>121511</v>
+        <v>121111</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7322</v>
       </c>
@@ -1200,19 +1305,19 @@
         <v>121311</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H25">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
@@ -1221,38 +1326,41 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
       <c r="F26" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H26">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1260,54 +1368,54 @@
       <c r="D27" t="s">
         <v>12</v>
       </c>
-      <c r="E27" t="s">
-        <v>22</v>
-      </c>
       <c r="F27" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>121511</v>
+        <v>122011</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
       <c r="F28" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>7322</v>
       </c>
       <c r="B29">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1316,24 +1424,24 @@
         <v>12</v>
       </c>
       <c r="F29" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" t="s">
         <v>17</v>
       </c>
-      <c r="I29" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>7322</v>
       </c>
       <c r="B30">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -1341,20 +1449,23 @@
       <c r="D30" t="s">
         <v>12</v>
       </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
       <c r="F30" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H30">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>7322</v>
       </c>
@@ -1362,30 +1473,30 @@
         <v>121411</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H31">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7322</v>
       </c>
       <c r="B32">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1393,54 +1504,54 @@
       <c r="D32" t="s">
         <v>12</v>
       </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
       <c r="F32" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H32">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7322</v>
+      </c>
+      <c r="B33">
+        <v>121511</v>
+      </c>
+      <c r="C33">
         <v>1</v>
       </c>
-      <c r="I32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46146</v>
+      </c>
+      <c r="H33">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33">
-        <v>7322</v>
-      </c>
-      <c r="B33">
-        <v>121311</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="1">
-        <v>46145</v>
-      </c>
-      <c r="H33">
-        <v>3</v>
-      </c>
-      <c r="I33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>7322</v>
       </c>
       <c r="B34">
-        <v>121411</v>
+        <v>121111</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1449,45 +1560,45 @@
         <v>12</v>
       </c>
       <c r="F34" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="I34" t="s">
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>7322</v>
       </c>
       <c r="B35">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="I35" t="s">
         <v>13</v>
       </c>
       <c r="J35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>7322</v>
       </c>
@@ -1495,16 +1606,16 @@
         <v>121411</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="F36" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="I36" t="s">
         <v>13</v>
@@ -1513,7 +1624,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>7322</v>
       </c>
@@ -1521,68 +1632,74 @@
         <v>122011</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
+      <c r="E37" t="s">
+        <v>65</v>
+      </c>
       <c r="F37" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J37" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>7322</v>
       </c>
       <c r="B38">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
       <c r="F38" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>7322</v>
       </c>
       <c r="B39">
-        <v>121311</v>
+        <v>121411</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F39" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -1591,199 +1708,326 @@
         <v>20</v>
       </c>
       <c r="J39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>7322</v>
+      </c>
+      <c r="B40">
+        <v>121111</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>7322</v>
+      </c>
+      <c r="B41">
+        <v>121411</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>7322</v>
+      </c>
+      <c r="B42">
+        <v>122011</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>7322</v>
+      </c>
+      <c r="B43">
+        <v>122011</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>7322</v>
+      </c>
+      <c r="B44">
+        <v>121311</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6">
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6">
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6">
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6">
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6">
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6">
+    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6">
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6">
+    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6">
+    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6">
+    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6">
+    <row r="59" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6">
+    <row r="60" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6">
+    <row r="61" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6">
+    <row r="62" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6">
+    <row r="63" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6">
+    <row r="64" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6">
+    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6">
+    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6">
+    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6">
+    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6">
+    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6">
+    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6">
+    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6">
+    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6">
+    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6">
+    <row r="74" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6">
+    <row r="75" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6">
+    <row r="76" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6">
+    <row r="77" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6">
+    <row r="78" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6">
+    <row r="79" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6">
+    <row r="80" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6">
+    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6">
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6">
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6">
+    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6">
+    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6">
+    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6">
+    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6">
+    <row r="88" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6">
+    <row r="89" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6">
+    <row r="90" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6">
+    <row r="91" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6">
+    <row r="92" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6">
+    <row r="93" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6">
+    <row r="94" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6">
+    <row r="95" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6">
+    <row r="96" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6">
+    <row r="97" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6">
+    <row r="98" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6">
+    <row r="99" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6">
+    <row r="100" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6">
+    <row r="101" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6">
+    <row r="102" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="6:6">
+    <row r="103" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F103" s="1"/>
     </row>
   </sheetData>
@@ -1794,12 +2038,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DED6C4F-4D8C-4EB4-A867-819126E7A3D9}">
   <dimension ref="A1:L91"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1837,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7322</v>
       </c>
@@ -1845,16 +2089,16 @@
         <v>121111</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1863,7 +2107,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7322</v>
       </c>
@@ -1871,16 +2115,16 @@
         <v>121411</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -1889,12 +2133,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>7322</v>
       </c>
       <c r="B4">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1903,19 +2147,19 @@
         <v>25</v>
       </c>
       <c r="F4" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7322</v>
       </c>
@@ -1923,39 +2167,39 @@
         <v>122011</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7322</v>
       </c>
       <c r="B6">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1964,10 +2208,10 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7322</v>
       </c>
@@ -1975,82 +2219,85 @@
         <v>121411</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="1">
+        <v>46154</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7322</v>
+      </c>
+      <c r="B8">
+        <v>121111</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1">
         <v>46153</v>
       </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
-        <v>7322</v>
-      </c>
-      <c r="B8">
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7322</v>
+      </c>
+      <c r="B9">
         <v>122011</v>
       </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46152</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
-        <v>7322</v>
-      </c>
-      <c r="B9">
-        <v>121411</v>
-      </c>
       <c r="C9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
       <c r="F9" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7322</v>
       </c>
       <c r="B10">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2059,19 +2306,19 @@
         <v>25</v>
       </c>
       <c r="F10" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7322</v>
       </c>
@@ -2079,25 +2326,28 @@
         <v>121411</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
       <c r="F11" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7322</v>
       </c>
@@ -2105,163 +2355,175 @@
         <v>122011</v>
       </c>
       <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46152</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7322</v>
+      </c>
+      <c r="B13">
+        <v>121411</v>
+      </c>
+      <c r="C13">
         <v>7</v>
       </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46151</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>7322</v>
+      </c>
+      <c r="B14">
+        <v>121111</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1">
         <v>46150</v>
       </c>
-      <c r="H12">
+      <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7322</v>
+      </c>
+      <c r="B15">
+        <v>121411</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7322</v>
+      </c>
+      <c r="B16">
+        <v>122011</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H16">
         <v>2</v>
       </c>
-      <c r="I12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13">
-        <v>7322</v>
-      </c>
-      <c r="B13">
-        <v>122011</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14">
-        <v>7322</v>
-      </c>
-      <c r="B14">
-        <v>121411</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15">
-        <v>7322</v>
-      </c>
-      <c r="B15">
-        <v>121511</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H15">
-        <v>13</v>
-      </c>
-      <c r="I15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16">
-        <v>7322</v>
-      </c>
-      <c r="B16">
-        <v>121411</v>
-      </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H16">
-        <v>4</v>
-      </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>7322</v>
       </c>
       <c r="B17">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46149</v>
+      </c>
+      <c r="H17">
         <v>3</v>
       </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
       <c r="I17" t="s">
         <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>7322</v>
       </c>
       <c r="B18">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2269,37 +2531,40 @@
       <c r="D18" t="s">
         <v>25</v>
       </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
       <c r="F18" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>7322</v>
       </c>
       <c r="B19">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="H19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I19" t="s">
         <v>13</v>
@@ -2308,33 +2573,36 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
       </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
       <c r="F20" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7322</v>
       </c>
@@ -2342,19 +2610,19 @@
         <v>121311</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
@@ -2363,64 +2631,70 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7322</v>
       </c>
       <c r="B22">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
       </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
       <c r="F22" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
       </c>
       <c r="F23" s="1">
         <v>46147</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I23" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7322</v>
       </c>
       <c r="B24">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2429,24 +2703,24 @@
         <v>25</v>
       </c>
       <c r="F24" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7322</v>
       </c>
       <c r="B25">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2454,54 +2728,57 @@
       <c r="D25" t="s">
         <v>25</v>
       </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
       <c r="F25" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H25">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>121311</v>
+        <v>121411</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2510,27 +2787,27 @@
         <v>25</v>
       </c>
       <c r="F27" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H27">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>121511</v>
+        <v>121111</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
@@ -2539,21 +2816,21 @@
         <v>46146</v>
       </c>
       <c r="H28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>7322</v>
       </c>
       <c r="B29">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -2561,25 +2838,28 @@
       <c r="D29" t="s">
         <v>25</v>
       </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
       <c r="F29" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>7322</v>
       </c>
       <c r="B30">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2587,51 +2867,57 @@
       <c r="D30" t="s">
         <v>25</v>
       </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
       <c r="F30" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>7322</v>
       </c>
       <c r="B31">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
       </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
       <c r="F31" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7322</v>
       </c>
       <c r="B32">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2640,10 +2926,10 @@
         <v>25</v>
       </c>
       <c r="F32" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
@@ -2652,181 +2938,282 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="6:6">
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="6:6">
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="6:6">
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="6:6">
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="6:6">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7322</v>
+      </c>
+      <c r="B33">
+        <v>122011</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7322</v>
+      </c>
+      <c r="B34">
+        <v>121411</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7322</v>
+      </c>
+      <c r="B35">
+        <v>121111</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7322</v>
+      </c>
+      <c r="B36">
+        <v>122011</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6">
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6">
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6">
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6">
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6">
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6">
+    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6">
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6">
+    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6">
+    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6">
+    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6">
+    <row r="59" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6">
+    <row r="60" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6">
+    <row r="61" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6">
+    <row r="62" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6">
+    <row r="63" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6">
+    <row r="64" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6">
+    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6">
+    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6">
+    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6">
+    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6">
+    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6">
+    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6">
+    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6">
+    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6">
+    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6">
+    <row r="74" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6">
+    <row r="75" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6">
+    <row r="76" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6">
+    <row r="77" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6">
+    <row r="78" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6">
+    <row r="79" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6">
+    <row r="80" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6">
+    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6">
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6">
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6">
+    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6">
+    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6">
+    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6">
+    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6">
+    <row r="88" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6">
+    <row r="89" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6">
+    <row r="90" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6">
+    <row r="91" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F91" s="1"/>
     </row>
   </sheetData>
@@ -2837,7 +3224,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E012F18-A142-4E22-97FA-EA6D909BC879}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.140625" bestFit="1" customWidth="1"/>
@@ -2845,7 +3232,7 @@
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2862,7 +3249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>121111</v>
       </c>
@@ -2879,7 +3266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>121311</v>
       </c>
@@ -2896,7 +3283,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>121411</v>
       </c>
@@ -2913,7 +3300,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>121511</v>
       </c>
@@ -2930,7 +3317,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>122011</v>
       </c>

--- a/data/auxiliar.xlsx
+++ b/data/auxiliar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailadventistas-my.sharepoint.com/personal/daniel_llaca_adventistas_org/Documents/INFORME JUNTAS/MENSUAL Y DIARIO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABF272D-2AE5-4215-B781-416F3BE4B778}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{BDD2B5C6-2AD7-4091-9D58-3AAC28D5444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C74A73F-D862-49E3-8D39-1406ABFD3716}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-2580" windowWidth="38640" windowHeight="21120" xr2:uid="{9F8F2C5A-F36E-41DE-A9AC-0765B5EE11E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="85">
   <si>
     <t>Entidad</t>
   </si>
@@ -251,6 +251,51 @@
   </si>
   <si>
     <t>RV 28</t>
+  </si>
+  <si>
+    <t>jose.irureta@adventistas.org</t>
+  </si>
+  <si>
+    <t>RV 40</t>
+  </si>
+  <si>
+    <t>RV 46</t>
+  </si>
+  <si>
+    <t>RV 39</t>
+  </si>
+  <si>
+    <t>RV 43</t>
+  </si>
+  <si>
+    <t>RV 42</t>
+  </si>
+  <si>
+    <t>RV 52</t>
+  </si>
+  <si>
+    <t>RV 41</t>
+  </si>
+  <si>
+    <t>RV 51</t>
+  </si>
+  <si>
+    <t>RV 50</t>
+  </si>
+  <si>
+    <t>RV 49</t>
+  </si>
+  <si>
+    <t>RV 48</t>
+  </si>
+  <si>
+    <t>RV 47</t>
+  </si>
+  <si>
+    <t>RV 44</t>
+  </si>
+  <si>
+    <t>RV 45</t>
   </si>
 </sst>
 </file>
@@ -686,25 +731,25 @@
         <v>7322</v>
       </c>
       <c r="B2">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -712,25 +757,25 @@
         <v>7322</v>
       </c>
       <c r="B3">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -738,25 +783,25 @@
         <v>7322</v>
       </c>
       <c r="B4">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -764,10 +809,10 @@
         <v>7322</v>
       </c>
       <c r="B5">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -776,13 +821,13 @@
         <v>46155</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -790,28 +835,25 @@
         <v>7322</v>
       </c>
       <c r="B6">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
       <c r="F6" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -819,25 +861,25 @@
         <v>7322</v>
       </c>
       <c r="B7">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -848,19 +890,22 @@
         <v>121311</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
       <c r="F8" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -871,25 +916,25 @@
         <v>7322</v>
       </c>
       <c r="B9">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -897,25 +942,28 @@
         <v>7322</v>
       </c>
       <c r="B10">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
       <c r="F10" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -923,25 +971,25 @@
         <v>7322</v>
       </c>
       <c r="B11">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -949,28 +997,28 @@
         <v>7322</v>
       </c>
       <c r="B12">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -981,22 +1029,25 @@
         <v>121411</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
       <c r="F13" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1004,28 +1055,25 @@
         <v>7322</v>
       </c>
       <c r="B14">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
       <c r="F14" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1033,28 +1081,28 @@
         <v>7322</v>
       </c>
       <c r="B15">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F15" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1062,25 +1110,28 @@
         <v>7322</v>
       </c>
       <c r="B16">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46153</v>
+      </c>
+      <c r="H16">
         <v>8</v>
       </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46151</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1088,25 +1139,28 @@
         <v>7322</v>
       </c>
       <c r="B17">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
       <c r="F17" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H17">
         <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1114,25 +1168,28 @@
         <v>7322</v>
       </c>
       <c r="B18">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
       <c r="F18" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1143,25 +1200,25 @@
         <v>122011</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F19" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I19" t="s">
         <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1169,22 +1226,25 @@
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
       <c r="F20" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1195,28 +1255,25 @@
         <v>7322</v>
       </c>
       <c r="B21">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H21">
         <v>7</v>
       </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H21">
-        <v>6</v>
-      </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1227,22 +1284,25 @@
         <v>121411</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
       <c r="F22" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1250,22 +1310,25 @@
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C23">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H23">
         <v>5</v>
       </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H23">
-        <v>7</v>
-      </c>
       <c r="I23" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -1276,25 +1339,25 @@
         <v>7322</v>
       </c>
       <c r="B24">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1302,28 +1365,28 @@
         <v>7322</v>
       </c>
       <c r="B25">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1331,7 +1394,7 @@
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -1340,13 +1403,13 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F26" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
@@ -1360,25 +1423,28 @@
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
+      <c r="E27" t="s">
+        <v>82</v>
+      </c>
       <c r="F27" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1386,28 +1452,25 @@
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="E28" t="s">
-        <v>64</v>
-      </c>
       <c r="F28" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H28">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1415,25 +1478,28 @@
         <v>7322</v>
       </c>
       <c r="B29">
-        <v>121511</v>
+        <v>121311</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
       <c r="F29" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1441,28 +1507,28 @@
         <v>7322</v>
       </c>
       <c r="B30">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F30" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H30">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I30" t="s">
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1470,10 +1536,10 @@
         <v>7322</v>
       </c>
       <c r="B31">
-        <v>121411</v>
+        <v>121111</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
@@ -1482,13 +1548,13 @@
         <v>46147</v>
       </c>
       <c r="H31">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I31" t="s">
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1496,28 +1562,28 @@
         <v>7322</v>
       </c>
       <c r="B32">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="F32" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1528,16 +1594,16 @@
         <v>121511</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I33" t="s">
         <v>13</v>
@@ -1551,25 +1617,28 @@
         <v>7322</v>
       </c>
       <c r="B34">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
       <c r="F34" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H34">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1577,7 +1646,7 @@
         <v>7322</v>
       </c>
       <c r="B35">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1586,16 +1655,16 @@
         <v>12</v>
       </c>
       <c r="F35" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H35">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
         <v>13</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1603,7 +1672,7 @@
         <v>7322</v>
       </c>
       <c r="B36">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -1611,17 +1680,20 @@
       <c r="D36" t="s">
         <v>12</v>
       </c>
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
       <c r="F36" s="1">
         <v>46146</v>
       </c>
       <c r="H36">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1629,25 +1701,22 @@
         <v>7322</v>
       </c>
       <c r="B37">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
-      <c r="E37" t="s">
-        <v>65</v>
-      </c>
       <c r="F37" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J37" t="s">
         <v>17</v>
@@ -1658,7 +1727,7 @@
         <v>7322</v>
       </c>
       <c r="B38">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1666,20 +1735,17 @@
       <c r="D38" t="s">
         <v>12</v>
       </c>
-      <c r="E38" t="s">
-        <v>23</v>
-      </c>
       <c r="F38" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -1687,28 +1753,28 @@
         <v>7322</v>
       </c>
       <c r="B39">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="F39" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="I39" t="s">
         <v>20</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1716,25 +1782,28 @@
         <v>7322</v>
       </c>
       <c r="B40">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
       <c r="F40" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="I40" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1742,22 +1811,22 @@
         <v>7322</v>
       </c>
       <c r="B41">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H41">
         <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" s="1">
-        <v>46144</v>
-      </c>
-      <c r="H41">
-        <v>2</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
@@ -1771,7 +1840,7 @@
         <v>7322</v>
       </c>
       <c r="B42">
-        <v>122011</v>
+        <v>121311</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1780,19 +1849,19 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F42" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="s">
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -1800,22 +1869,22 @@
         <v>7322</v>
       </c>
       <c r="B43">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H43">
         <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" t="s">
-        <v>69</v>
-      </c>
-      <c r="F43" s="1">
-        <v>46143</v>
-      </c>
-      <c r="H43">
-        <v>4</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
@@ -1829,7 +1898,7 @@
         <v>7322</v>
       </c>
       <c r="B44">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1837,33 +1906,134 @@
       <c r="D44" t="s">
         <v>12</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>7322</v>
+      </c>
+      <c r="B45">
+        <v>121411</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>7322</v>
+      </c>
+      <c r="B46">
+        <v>122011</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="1">
+        <v>46144</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>7322</v>
+      </c>
+      <c r="B47">
+        <v>122011</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>7322</v>
+      </c>
+      <c r="B48">
+        <v>121311</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F48" s="1">
         <v>46143</v>
       </c>
-      <c r="H44">
+      <c r="H48">
         <v>1</v>
       </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="I48" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F48" s="1"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F49" s="1"/>
@@ -2086,25 +2256,25 @@
         <v>7322</v>
       </c>
       <c r="B2">
-        <v>121111</v>
+        <v>121411</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2112,25 +2282,25 @@
         <v>7322</v>
       </c>
       <c r="B3">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,25 +2308,25 @@
         <v>7322</v>
       </c>
       <c r="B4">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2164,10 +2334,10 @@
         <v>7322</v>
       </c>
       <c r="B5">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -2176,13 +2346,13 @@
         <v>46155</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2193,16 +2363,16 @@
         <v>121111</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -2219,16 +2389,16 @@
         <v>121411</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
@@ -2242,7 +2412,7 @@
         <v>7322</v>
       </c>
       <c r="B8">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -2250,17 +2420,20 @@
       <c r="D8" t="s">
         <v>25</v>
       </c>
+      <c r="E8" t="s">
+        <v>71</v>
+      </c>
       <c r="F8" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2271,25 +2444,22 @@
         <v>122011</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2297,16 +2467,16 @@
         <v>7322</v>
       </c>
       <c r="B10">
-        <v>121311</v>
+        <v>121111</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -2315,7 +2485,7 @@
         <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2326,25 +2496,25 @@
         <v>121411</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F11" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2352,28 +2522,25 @@
         <v>7322</v>
       </c>
       <c r="B12">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
       <c r="F12" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2381,28 +2548,28 @@
         <v>7322</v>
       </c>
       <c r="B13">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
         <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2410,7 +2577,7 @@
         <v>7322</v>
       </c>
       <c r="B14">
-        <v>121111</v>
+        <v>121311</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -2418,17 +2585,20 @@
       <c r="D14" t="s">
         <v>25</v>
       </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
       <c r="F14" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
         <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2439,25 +2609,25 @@
         <v>121411</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2468,25 +2638,25 @@
         <v>122011</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2494,28 +2664,28 @@
         <v>7322</v>
       </c>
       <c r="B17">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2523,28 +2693,25 @@
         <v>7322</v>
       </c>
       <c r="B18">
-        <v>121411</v>
+        <v>121111</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
       <c r="F18" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2552,25 +2719,28 @@
         <v>7322</v>
       </c>
       <c r="B19">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46150</v>
+      </c>
+      <c r="H19">
         <v>3</v>
       </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46149</v>
-      </c>
-      <c r="H19">
-        <v>13</v>
-      </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2578,22 +2748,22 @@
         <v>7322</v>
       </c>
       <c r="B20">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F20" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" t="s">
         <v>20</v>
@@ -2607,28 +2777,28 @@
         <v>7322</v>
       </c>
       <c r="B21">
-        <v>121311</v>
+        <v>122011</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46149</v>
+      </c>
+      <c r="H21">
         <v>3</v>
       </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46148</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
       <c r="I21" t="s">
         <v>20</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2636,7 +2806,7 @@
         <v>7322</v>
       </c>
       <c r="B22">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2645,19 +2815,19 @@
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2665,25 +2835,22 @@
         <v>7322</v>
       </c>
       <c r="B23">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
       </c>
-      <c r="E23" t="s">
-        <v>50</v>
-      </c>
       <c r="F23" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -2694,25 +2861,28 @@
         <v>7322</v>
       </c>
       <c r="B24">
-        <v>121511</v>
+        <v>121411</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
       </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
       <c r="F24" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2723,19 +2893,19 @@
         <v>121311</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
@@ -2749,28 +2919,28 @@
         <v>7322</v>
       </c>
       <c r="B26">
-        <v>121411</v>
+        <v>122011</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2778,25 +2948,28 @@
         <v>7322</v>
       </c>
       <c r="B27">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>50</v>
       </c>
       <c r="F27" s="1">
         <v>46147</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2804,7 +2977,7 @@
         <v>7322</v>
       </c>
       <c r="B28">
-        <v>121111</v>
+        <v>121511</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -2813,16 +2986,16 @@
         <v>25</v>
       </c>
       <c r="F28" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2830,7 +3003,7 @@
         <v>7322</v>
       </c>
       <c r="B29">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -2839,19 +3012,19 @@
         <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H29">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I29" t="s">
         <v>20</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2859,28 +3032,28 @@
         <v>7322</v>
       </c>
       <c r="B30">
-        <v>121311</v>
+        <v>121411</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F30" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="s">
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2888,7 +3061,7 @@
         <v>7322</v>
       </c>
       <c r="B31">
-        <v>122011</v>
+        <v>121111</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -2896,20 +3069,17 @@
       <c r="D31" t="s">
         <v>25</v>
       </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
       <c r="F31" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="H31">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2917,10 +3087,10 @@
         <v>7322</v>
       </c>
       <c r="B32">
-        <v>121511</v>
+        <v>121111</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
@@ -2929,13 +3099,13 @@
         <v>46146</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2943,7 +3113,7 @@
         <v>7322</v>
       </c>
       <c r="B33">
-        <v>122011</v>
+        <v>121411</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -2952,19 +3122,19 @@
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="I33" t="s">
         <v>20</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2972,7 +3142,7 @@
         <v>7322</v>
       </c>
       <c r="B34">
-        <v>121411</v>
+        <v>121311</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2981,19 +3151,19 @@
         <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F34" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34" t="s">
         <v>20</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3001,25 +3171,28 @@
         <v>7322</v>
       </c>
       <c r="B35">
-        <v>121111</v>
+        <v>122011</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
       </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
       <c r="F35" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3027,7 +3200,7 @@
         <v>7322</v>
       </c>
       <c r="B36">
-        <v>122011</v>
+        <v>121511</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3035,33 +3208,131 @@
       <c r="D36" t="s">
         <v>25</v>
       </c>
-      <c r="E36" t="s">
-        <v>56</v>
-      </c>
       <c r="F36" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F37" s="1"/>
+      <c r="A37">
+        <v>7322</v>
+      </c>
+      <c r="B37">
+        <v>122011</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F38" s="1"/>
+      <c r="A38">
+        <v>7322</v>
+      </c>
+      <c r="B38">
+        <v>121411</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F39" s="1"/>
+      <c r="A39">
+        <v>7322</v>
+      </c>
+      <c r="B39">
+        <v>121111</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46145</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F40" s="1"/>
+      <c r="A40">
+        <v>7322</v>
+      </c>
+      <c r="B40">
+        <v>122011</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46143</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F41" s="1"/>
